--- a/data/trans_dic/P1414-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P1414-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,27</t>
+          <t>0,15; 1,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,92</t>
+          <t>0,14; 1,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,02</t>
+          <t>2,24; 5,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,6</t>
+          <t>2,51; 5,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 4,45</t>
+          <t>2,43; 4,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,53</t>
+          <t>1,16; 2,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,89</t>
+          <t>1,45; 3,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,8</t>
+          <t>1,48; 2,75</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,84</t>
+          <t>0,1; 0,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,99</t>
+          <t>1,26; 3,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,27</t>
+          <t>2,59; 5,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 5,76</t>
+          <t>3,62; 5,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,75</t>
+          <t>0,74; 1,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,9</t>
+          <t>1,52; 2,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,73</t>
+          <t>1,87; 2,92</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,35</t>
+          <t>0,14; 1,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,45</t>
+          <t>1,19; 3,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,72</t>
+          <t>2,13; 4,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,82</t>
+          <t>2,45; 4,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,92</t>
+          <t>0,66; 1,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,61</t>
+          <t>1,16; 2,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,36</t>
+          <t>1,42; 2,6</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,3</t>
+          <t>0,21; 1,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,06</t>
+          <t>0,19; 1,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,16</t>
+          <t>2,12; 4,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,56</t>
+          <t>2,31; 4,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,64</t>
+          <t>3,99; 6,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,38</t>
+          <t>1,17; 2,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,78</t>
+          <t>1,39; 2,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,3</t>
+          <t>2,31; 3,59</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1123,42 +1123,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,74</t>
+          <t>0,23; 0,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,72</t>
+          <t>0,25; 0,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,19</t>
+          <t>2,1; 3,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,19</t>
+          <t>2,95; 4,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,43</t>
+          <t>3,69; 4,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,75</t>
+          <t>1,16; 1,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,38</t>
+          <t>1,7; 2,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,49</t>
+          <t>2,06; 2,62</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22377</t>
+          <t>23676</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26613</t>
+          <t>28098</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5376</t>
+          <t>0; 5433</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1021; 8545</t>
+          <t>1017; 8498</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>955; 12220</t>
+          <t>958; 12879</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14626; 35026</t>
+          <t>15631; 35260</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17631; 37654</t>
+          <t>16875; 37425</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16374; 29947</t>
+          <t>17727; 31851</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16358; 35444</t>
+          <t>16222; 35985</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19460; 38949</t>
+          <t>19599; 41210</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19320; 36684</t>
+          <t>20976; 39112</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43891</t>
+          <t>47987</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>45589</t>
+          <t>49636</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1011; 8589</t>
+          <t>1008; 7916</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1008; 8659</t>
+          <t>1015; 8658</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6475</t>
+          <t>0; 5510</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13018; 30800</t>
+          <t>13010; 31940</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29243; 54938</t>
+          <t>27046; 54117</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35229; 54972</t>
+          <t>38631; 60827</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15301; 35809</t>
+          <t>15101; 35810</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31228; 59818</t>
+          <t>31336; 57773</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29931; 58521</t>
+          <t>39482; 61694</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24172</t>
+          <t>27249</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>31152</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5246</t>
+          <t>0; 6046</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6886</t>
+          <t>0; 7059</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1091; 9490</t>
+          <t>1114; 9698</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9253; 26786</t>
+          <t>9260; 27544</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16484; 37046</t>
+          <t>16715; 37044</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12206; 35531</t>
+          <t>19722; 35838</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10174; 29465</t>
+          <t>10160; 28723</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18032; 40275</t>
+          <t>17943; 39622</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17648; 38426</t>
+          <t>22848; 41701</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49170</t>
+          <t>56030</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>53928</t>
+          <t>60823</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 7254</t>
+          <t>0; 6242</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1924; 12221</t>
+          <t>1943; 12769</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1546; 9754</t>
+          <t>1831; 10435</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21791; 43728</t>
+          <t>22293; 45721</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23644; 47646</t>
+          <t>24149; 48592</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37957; 61417</t>
+          <t>44434; 68364</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24129; 47482</t>
+          <t>23414; 46580</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28765; 55006</t>
+          <t>27458; 53833</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43065; 66341</t>
+          <t>48623; 75391</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>139611</t>
+          <t>154942</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>153915</t>
+          <t>169709</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3156; 14751</t>
+          <t>3101; 14843</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7736; 24968</t>
+          <t>7964; 23343</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8274; 24721</t>
+          <t>8751; 24926</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74465; 113465</t>
+          <t>74492; 112317</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>103445; 148355</t>
+          <t>104683; 152413</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>112384; 161418</t>
+          <t>137214; 175174</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81633; 122298</t>
+          <t>80983; 122212</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>117704; 165178</t>
+          <t>118219; 163638</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>129157; 176545</t>
+          <t>149484; 190076</t>
         </is>
       </c>
     </row>
